--- a/results/0916-all/川鄂湘黔边境山地林农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/川鄂湘黔边境山地林农牧区/tech_selected_summary.xlsx
@@ -250,190 +250,190 @@
     <t>秭归县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -469,10 +469,10 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 309596073.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>309596073.87</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -586,16 +586,16 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 217236259.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 939651.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 59531795.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 1259157.87</t>
+    <t>217236259.15</t>
+  </si>
+  <si>
+    <t>939651.44</t>
+  </si>
+  <si>
+    <t>59531795.68</t>
+  </si>
+  <si>
+    <t>1259157.87</t>
   </si>
   <si>
     <t>Composting_pig</t>
@@ -610,16 +610,16 @@
     <t>4R(Right time)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 296180794.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 2181257.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 663114.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 16271881.41</t>
+    <t>296180794.33</t>
+  </si>
+  <si>
+    <t>2181257.67</t>
+  </si>
+  <si>
+    <t>663114.48</t>
+  </si>
+  <si>
+    <t>16271881.41</t>
   </si>
   <si>
     <t>Slatted floor vs Solid floor_beef cattle</t>
@@ -634,19 +634,19 @@
     <t>4R(Right rate)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 271831421.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 160342500.91</t>
-  </si>
-  <si>
-    <t>总经济成本: -4647605.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 68395478.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 63404214.17</t>
+    <t>271831421.76</t>
+  </si>
+  <si>
+    <t>160342500.91</t>
+  </si>
+  <si>
+    <t>-4647605.11</t>
+  </si>
+  <si>
+    <t>68395478.09</t>
+  </si>
+  <si>
+    <t>63404214.17</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -664,7 +664,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 153416119.65</t>
+    <t>153416119.65</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -682,37 +682,37 @@
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 677820345.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 37087951.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 25813339.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 9483334.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 99094013.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 109053002.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 11648666.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 42273875.00</t>
+    <t>677820345.15</t>
+  </si>
+  <si>
+    <t>37087951.81</t>
+  </si>
+  <si>
+    <t>25813339.45</t>
+  </si>
+  <si>
+    <t>9483334.41</t>
+  </si>
+  <si>
+    <t>99094013.91</t>
+  </si>
+  <si>
+    <t>109053002.53</t>
+  </si>
+  <si>
+    <t>11648666.69</t>
+  </si>
+  <si>
+    <t>42273875.00</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 348634798.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 112996587.34</t>
+    <t>348634798.05</t>
+  </si>
+  <si>
+    <t>112996587.34</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -742,25 +742,25 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 449827042.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 14460113.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 2315784.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 2436426.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 38831537.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 32696796.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 3292137.91</t>
+    <t>449827042.80</t>
+  </si>
+  <si>
+    <t>14460113.50</t>
+  </si>
+  <si>
+    <t>2315784.13</t>
+  </si>
+  <si>
+    <t>2436426.11</t>
+  </si>
+  <si>
+    <t>38831537.03</t>
+  </si>
+  <si>
+    <t>32696796.46</t>
+  </si>
+  <si>
+    <t>3292137.91</t>
   </si>
   <si>
     <t>Nitrate_sheep &amp; goat</t>
@@ -778,10 +778,10 @@
     <t>Feedstock adjustment_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 250602062.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 25223112.45</t>
+    <t>250602062.03</t>
+  </si>
+  <si>
+    <t>25223112.45</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
@@ -790,16 +790,16 @@
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 144498361.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 64438716.14</t>
+    <t>144498361.45</t>
+  </si>
+  <si>
+    <t>64438716.14</t>
   </si>
   <si>
     <t>biochar_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 273522199.17</t>
+    <t>273522199.17</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -847,7 +847,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 735447295.81</t>
+    <t>735447295.81</t>
   </si>
   <si>
     <t>Bioflilter_poultry</t>
@@ -859,25 +859,25 @@
     <t>4R(Right place)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 217678755.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 132292628.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 2843982.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 1984993.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 26893070.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 4224215.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 88617551.98</t>
+    <t>217678755.12</t>
+  </si>
+  <si>
+    <t>132292628.35</t>
+  </si>
+  <si>
+    <t>2843982.66</t>
+  </si>
+  <si>
+    <t>1984993.32</t>
+  </si>
+  <si>
+    <t>26893070.76</t>
+  </si>
+  <si>
+    <t>4224215.43</t>
+  </si>
+  <si>
+    <t>88617551.98</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_maize</t>
@@ -886,22 +886,22 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 330118537.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 115093474.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 63677985.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 4620741.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 54109550.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 114367857.03</t>
+    <t>330118537.64</t>
+  </si>
+  <si>
+    <t>115093474.57</t>
+  </si>
+  <si>
+    <t>63677985.61</t>
+  </si>
+  <si>
+    <t>4620741.20</t>
+  </si>
+  <si>
+    <t>54109550.15</t>
+  </si>
+  <si>
+    <t>114367857.03</t>
   </si>
 </sst>
 </file>
